--- a/PAMaap/app/archives/XLXS_IMPORT/ALIMENTADORES/Servidores_Fisicos.xlsx
+++ b/PAMaap/app/archives/XLXS_IMPORT/ALIMENTADORES/Servidores_Fisicos.xlsx
@@ -5,25 +5,38 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlos.bedoya\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlos.bedoya\Documents\Documentacion\Equipo Infra\Scripts Python\autompython\PAMaap\app\archives\XLXS_IMPORT\ALIMENTADORES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{882E4586-0C64-4532-9602-203BC63F4700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F72295B6-EF77-422D-BA26-46165D2EE92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1260" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{800DEBD1-45ED-4A4C-9D0A-93ACBEBB2184}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{800DEBD1-45ED-4A4C-9D0A-93ACBEBB2184}"/>
   </bookViews>
   <sheets>
     <sheet name="Servidores_Fisicos" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Servidores_Fisicos!$A$1:$E$300</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Servidores_Fisicos!$A$1:$E$277</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="572">
   <si>
     <t>Operating system</t>
   </si>
@@ -334,9 +347,6 @@
     <t>FYDH144</t>
   </si>
   <si>
-    <t>RedHatEnterprise</t>
-  </si>
-  <si>
     <t>DNADDSP08</t>
   </si>
   <si>
@@ -358,12 +368,6 @@
     <t>SRCAIDSTRPTL01</t>
   </si>
   <si>
-    <t>arlohsappsa01</t>
-  </si>
-  <si>
-    <t>RedHatEnterpriseServer</t>
-  </si>
-  <si>
     <t>SRSCSBAQDPP01</t>
   </si>
   <si>
@@ -394,18 +398,12 @@
     <t>5VQS2Z3</t>
   </si>
   <si>
-    <t>Red Hat Enterprise Linux release 8.10 (Ootpa)</t>
-  </si>
-  <si>
     <t>CM-ADCONNECTPDN</t>
   </si>
   <si>
     <t>0000-0001-9398-2752-2356-5949-90</t>
   </si>
   <si>
-    <t>srsaphccp01</t>
-  </si>
-  <si>
     <t>ARLBGAPRNTP01</t>
   </si>
   <si>
@@ -421,9 +419,6 @@
     <t>5486-9148-8108-4157-2023-8068-31</t>
   </si>
   <si>
-    <t>srmdebdpv01</t>
-  </si>
-  <si>
     <t>IPSADDSP13</t>
   </si>
   <si>
@@ -478,21 +473,12 @@
     <t>C2NRPX2</t>
   </si>
   <si>
-    <t>EPSMDEWLSIPSAP05</t>
-  </si>
-  <si>
     <t>SRSCMVSLDPP01</t>
   </si>
   <si>
     <t>GRVWDX2</t>
   </si>
   <si>
-    <t>srbogasgtuappp01</t>
-  </si>
-  <si>
-    <t>Red Hat Enterprise Linux Server release 7.9 (Maipo)</t>
-  </si>
-  <si>
     <t>SRADDSP09</t>
   </si>
   <si>
@@ -568,9 +554,6 @@
     <t>3XLCH04</t>
   </si>
   <si>
-    <t>srintcp08</t>
-  </si>
-  <si>
     <t>DNIATMBK01</t>
   </si>
   <si>
@@ -640,9 +623,6 @@
     <t>0000-0017-2646-4850-8083-4870-72</t>
   </si>
   <si>
-    <t>EPSMDEWLSIPSAP04</t>
-  </si>
-  <si>
     <t>DNBGPS01</t>
   </si>
   <si>
@@ -673,9 +653,6 @@
     <t>96Z1XB4</t>
   </si>
   <si>
-    <t>srncsrbksa03</t>
-  </si>
-  <si>
     <t>SRSCSARMDPP01</t>
   </si>
   <si>
@@ -784,9 +761,6 @@
     <t>F963DX3</t>
   </si>
   <si>
-    <t>srmdepenp</t>
-  </si>
-  <si>
     <t>DNBGHV15</t>
   </si>
   <si>
@@ -817,9 +791,6 @@
     <t>8Y05DP2</t>
   </si>
   <si>
-    <t>arlmdejoomlap10</t>
-  </si>
-  <si>
     <t>SRCTXSTFSA01</t>
   </si>
   <si>
@@ -955,9 +926,6 @@
     <t>D963DX3</t>
   </si>
   <si>
-    <t>srmdepend</t>
-  </si>
-  <si>
     <t>ARLADDSP11</t>
   </si>
   <si>
@@ -970,9 +938,6 @@
     <t>8678-9105-7297-6766-2723-6143-86</t>
   </si>
   <si>
-    <t>arlmdejoomlap09</t>
-  </si>
-  <si>
     <t>WIN-NQJULD9E3OP</t>
   </si>
   <si>
@@ -982,9 +947,6 @@
     <t>6JVW144</t>
   </si>
   <si>
-    <t>segmdewlsd02</t>
-  </si>
-  <si>
     <t>IPSRODCP14</t>
   </si>
   <si>
@@ -997,9 +959,6 @@
     <t>4YV3WP2</t>
   </si>
   <si>
-    <t>segmdewlsp19</t>
-  </si>
-  <si>
     <t>SRSCSALODPP01</t>
   </si>
   <si>
@@ -1024,9 +983,6 @@
     <t>5H95Z24</t>
   </si>
   <si>
-    <t>epswlsappsa01</t>
-  </si>
-  <si>
     <t>DNBGAPS01</t>
   </si>
   <si>
@@ -1099,9 +1055,6 @@
     <t>DDVLN23</t>
   </si>
   <si>
-    <t>arlmdejoomlal01clon</t>
-  </si>
-  <si>
     <t>SRSCSAGODPP01</t>
   </si>
   <si>
@@ -1135,9 +1088,6 @@
     <t>6R03XB4</t>
   </si>
   <si>
-    <t>segmdewlsp18</t>
-  </si>
-  <si>
     <t>SRADCLOUDDRP03</t>
   </si>
   <si>
@@ -1171,9 +1121,6 @@
     <t>MXQ52305W4</t>
   </si>
   <si>
-    <t>epsohsappsa01</t>
-  </si>
-  <si>
     <t>SRSCONZADPP01</t>
   </si>
   <si>
@@ -1297,9 +1244,6 @@
     <t>3MKCRN3</t>
   </si>
   <si>
-    <t>srsaphccq01</t>
-  </si>
-  <si>
     <t>SGADDSP24</t>
   </si>
   <si>
@@ -1318,12 +1262,6 @@
     <t>5KXJ3D4</t>
   </si>
   <si>
-    <t>segmdewlsp17</t>
-  </si>
-  <si>
-    <t>srbogbdstagiep01</t>
-  </si>
-  <si>
     <t>SGFILP01</t>
   </si>
   <si>
@@ -1336,9 +1274,6 @@
     <t>29ZX2Z3</t>
   </si>
   <si>
-    <t>EPSMDEWLSIPSAP06</t>
-  </si>
-  <si>
     <t>DNBGPS12</t>
   </si>
   <si>
@@ -1762,15 +1697,6 @@
     <t>CR27KD3</t>
   </si>
   <si>
-    <t>jarvis</t>
-  </si>
-  <si>
-    <t>Ubuntu 18.04</t>
-  </si>
-  <si>
-    <t>JBR3HQ2</t>
-  </si>
-  <si>
     <t>DNBGPS012</t>
   </si>
   <si>
@@ -1787,6 +1713,45 @@
   </si>
   <si>
     <t>Fisico</t>
+  </si>
+  <si>
+    <t>8 GB</t>
+  </si>
+  <si>
+    <t>16 GB</t>
+  </si>
+  <si>
+    <t>32 GB</t>
+  </si>
+  <si>
+    <t>24 GB</t>
+  </si>
+  <si>
+    <t>48 GB</t>
+  </si>
+  <si>
+    <t>64 GB</t>
+  </si>
+  <si>
+    <t>128 GB</t>
+  </si>
+  <si>
+    <t>12 GB</t>
+  </si>
+  <si>
+    <t>4 GB</t>
+  </si>
+  <si>
+    <t>28 GB</t>
+  </si>
+  <si>
+    <t>512 GB</t>
+  </si>
+  <si>
+    <t>49 GB</t>
+  </si>
+  <si>
+    <t>80 GB</t>
   </si>
 </sst>
 </file>
@@ -2681,7 +2646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A3679B1-22FB-4F47-82CA-80DBF18D622E}">
-  <dimension ref="A1:E300"/>
+  <dimension ref="A1:E277"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
@@ -2692,19 +2657,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>584</v>
+        <v>555</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>586</v>
+        <v>557</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>585</v>
+        <v>556</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>587</v>
+        <v>558</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -2714,8 +2679,8 @@
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2">
-        <v>8</v>
+      <c r="C2" t="s">
+        <v>559</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -2731,8 +2696,8 @@
       <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="C3">
-        <v>8</v>
+      <c r="C3" t="s">
+        <v>559</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -2748,8 +2713,8 @@
       <c r="B4" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>8</v>
+      <c r="C4" t="s">
+        <v>559</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -2765,8 +2730,8 @@
       <c r="B5" t="s">
         <v>3</v>
       </c>
-      <c r="C5">
-        <v>8</v>
+      <c r="C5" t="s">
+        <v>559</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -2782,8 +2747,8 @@
       <c r="B6" t="s">
         <v>3</v>
       </c>
-      <c r="C6">
-        <v>8</v>
+      <c r="C6" t="s">
+        <v>559</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -2799,8 +2764,8 @@
       <c r="B7" t="s">
         <v>3</v>
       </c>
-      <c r="C7">
-        <v>8</v>
+      <c r="C7" t="s">
+        <v>559</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -2816,8 +2781,8 @@
       <c r="B8" t="s">
         <v>18</v>
       </c>
-      <c r="C8">
-        <v>16</v>
+      <c r="C8" t="s">
+        <v>560</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -2833,8 +2798,8 @@
       <c r="B9" t="s">
         <v>3</v>
       </c>
-      <c r="C9">
-        <v>16</v>
+      <c r="C9" t="s">
+        <v>560</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -2850,8 +2815,8 @@
       <c r="B10" t="s">
         <v>3</v>
       </c>
-      <c r="C10">
-        <v>16</v>
+      <c r="C10" t="s">
+        <v>560</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -2867,8 +2832,8 @@
       <c r="B11" t="s">
         <v>12</v>
       </c>
-      <c r="C11">
-        <v>32</v>
+      <c r="C11" t="s">
+        <v>561</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -2884,8 +2849,8 @@
       <c r="B12" t="s">
         <v>12</v>
       </c>
-      <c r="C12">
-        <v>24</v>
+      <c r="C12" t="s">
+        <v>562</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -2901,8 +2866,8 @@
       <c r="B13" t="s">
         <v>3</v>
       </c>
-      <c r="C13">
-        <v>16</v>
+      <c r="C13" t="s">
+        <v>560</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2918,8 +2883,8 @@
       <c r="B14" t="s">
         <v>12</v>
       </c>
-      <c r="C14">
-        <v>24</v>
+      <c r="C14" t="s">
+        <v>562</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -2935,8 +2900,8 @@
       <c r="B15" t="s">
         <v>12</v>
       </c>
-      <c r="C15">
-        <v>32</v>
+      <c r="C15" t="s">
+        <v>561</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -2952,8 +2917,8 @@
       <c r="B16" t="s">
         <v>18</v>
       </c>
-      <c r="C16">
-        <v>16</v>
+      <c r="C16" t="s">
+        <v>560</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -2969,8 +2934,8 @@
       <c r="B17" t="s">
         <v>3</v>
       </c>
-      <c r="C17">
-        <v>16</v>
+      <c r="C17" t="s">
+        <v>560</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -2986,8 +2951,8 @@
       <c r="B18" t="s">
         <v>1</v>
       </c>
-      <c r="C18">
-        <v>16</v>
+      <c r="C18" t="s">
+        <v>560</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -3003,8 +2968,8 @@
       <c r="B19" t="s">
         <v>3</v>
       </c>
-      <c r="C19">
-        <v>16</v>
+      <c r="C19" t="s">
+        <v>560</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -3020,8 +2985,8 @@
       <c r="B20" t="s">
         <v>12</v>
       </c>
-      <c r="C20">
-        <v>48</v>
+      <c r="C20" t="s">
+        <v>563</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -3037,8 +3002,8 @@
       <c r="B21" t="s">
         <v>12</v>
       </c>
-      <c r="C21">
-        <v>48</v>
+      <c r="C21" t="s">
+        <v>563</v>
       </c>
       <c r="D21">
         <v>2</v>
@@ -3054,8 +3019,8 @@
       <c r="B22" t="s">
         <v>12</v>
       </c>
-      <c r="C22">
-        <v>24</v>
+      <c r="C22" t="s">
+        <v>562</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -3071,8 +3036,8 @@
       <c r="B23" t="s">
         <v>12</v>
       </c>
-      <c r="C23">
-        <v>32</v>
+      <c r="C23" t="s">
+        <v>561</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -3088,8 +3053,8 @@
       <c r="B24" t="s">
         <v>12</v>
       </c>
-      <c r="C24">
-        <v>24</v>
+      <c r="C24" t="s">
+        <v>562</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -3105,8 +3070,8 @@
       <c r="B25" t="s">
         <v>58</v>
       </c>
-      <c r="C25">
-        <v>8</v>
+      <c r="C25" t="s">
+        <v>559</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -3122,8 +3087,8 @@
       <c r="B26" t="s">
         <v>58</v>
       </c>
-      <c r="C26">
-        <v>8</v>
+      <c r="C26" t="s">
+        <v>559</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -3139,8 +3104,8 @@
       <c r="B27" t="s">
         <v>63</v>
       </c>
-      <c r="C27">
-        <v>16</v>
+      <c r="C27" t="s">
+        <v>560</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -3156,8 +3121,8 @@
       <c r="B28" t="s">
         <v>58</v>
       </c>
-      <c r="C28">
-        <v>64</v>
+      <c r="C28" t="s">
+        <v>564</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -3173,8 +3138,8 @@
       <c r="B29" t="s">
         <v>58</v>
       </c>
-      <c r="C29">
-        <v>64</v>
+      <c r="C29" t="s">
+        <v>564</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -3190,8 +3155,8 @@
       <c r="B30" t="s">
         <v>58</v>
       </c>
-      <c r="C30">
-        <v>64</v>
+      <c r="C30" t="s">
+        <v>564</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -3207,8 +3172,8 @@
       <c r="B31" t="s">
         <v>58</v>
       </c>
-      <c r="C31">
-        <v>64</v>
+      <c r="C31" t="s">
+        <v>564</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -3224,8 +3189,8 @@
       <c r="B32" t="s">
         <v>58</v>
       </c>
-      <c r="C32">
-        <v>64</v>
+      <c r="C32" t="s">
+        <v>564</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -3241,8 +3206,8 @@
       <c r="B33" t="s">
         <v>58</v>
       </c>
-      <c r="C33">
-        <v>64</v>
+      <c r="C33" t="s">
+        <v>564</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -3258,8 +3223,8 @@
       <c r="B34" t="s">
         <v>3</v>
       </c>
-      <c r="C34">
-        <v>32</v>
+      <c r="C34" t="s">
+        <v>561</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -3275,8 +3240,8 @@
       <c r="B35" t="s">
         <v>12</v>
       </c>
-      <c r="C35">
-        <v>32</v>
+      <c r="C35" t="s">
+        <v>561</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -3292,8 +3257,8 @@
       <c r="B36" t="s">
         <v>12</v>
       </c>
-      <c r="C36">
-        <v>32</v>
+      <c r="C36" t="s">
+        <v>561</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -3309,8 +3274,8 @@
       <c r="B37" t="s">
         <v>12</v>
       </c>
-      <c r="C37">
-        <v>24</v>
+      <c r="C37" t="s">
+        <v>562</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -3326,8 +3291,8 @@
       <c r="B38" t="s">
         <v>12</v>
       </c>
-      <c r="C38">
-        <v>24</v>
+      <c r="C38" t="s">
+        <v>562</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -3343,8 +3308,8 @@
       <c r="B39" t="s">
         <v>3</v>
       </c>
-      <c r="C39">
-        <v>16</v>
+      <c r="C39" t="s">
+        <v>560</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -3360,8 +3325,8 @@
       <c r="B40" t="s">
         <v>18</v>
       </c>
-      <c r="C40">
-        <v>32</v>
+      <c r="C40" t="s">
+        <v>561</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -3377,8 +3342,8 @@
       <c r="B41" t="s">
         <v>18</v>
       </c>
-      <c r="C41">
-        <v>32</v>
+      <c r="C41" t="s">
+        <v>561</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -3394,8 +3359,8 @@
       <c r="B42" t="s">
         <v>12</v>
       </c>
-      <c r="C42">
-        <v>32</v>
+      <c r="C42" t="s">
+        <v>561</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -3411,8 +3376,8 @@
       <c r="B43" t="s">
         <v>12</v>
       </c>
-      <c r="C43">
-        <v>32</v>
+      <c r="C43" t="s">
+        <v>561</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -3428,8 +3393,8 @@
       <c r="B44" t="s">
         <v>3</v>
       </c>
-      <c r="C44">
-        <v>16</v>
+      <c r="C44" t="s">
+        <v>560</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -3440,248 +3405,257 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>103</v>
+      </c>
+      <c r="B45" t="s">
+        <v>3</v>
+      </c>
+      <c r="C45" t="s">
+        <v>560</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45" t="s">
         <v>104</v>
-      </c>
-      <c r="B45" t="s">
-        <v>3</v>
-      </c>
-      <c r="C45">
-        <v>16</v>
-      </c>
-      <c r="D45">
-        <v>1</v>
-      </c>
-      <c r="E45" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>105</v>
+      </c>
+      <c r="B46" t="s">
+        <v>3</v>
+      </c>
+      <c r="C46" t="s">
+        <v>560</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46" t="s">
         <v>106</v>
-      </c>
-      <c r="B46" t="s">
-        <v>3</v>
-      </c>
-      <c r="C46">
-        <v>16</v>
-      </c>
-      <c r="D46">
-        <v>1</v>
-      </c>
-      <c r="E46" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>107</v>
+      </c>
+      <c r="B47" t="s">
+        <v>3</v>
+      </c>
+      <c r="C47" t="s">
+        <v>560</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47" t="s">
         <v>108</v>
-      </c>
-      <c r="B47" t="s">
-        <v>3</v>
-      </c>
-      <c r="C47">
-        <v>16</v>
-      </c>
-      <c r="D47">
-        <v>1</v>
-      </c>
-      <c r="E47" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>110</v>
+      </c>
+      <c r="B48" t="s">
+        <v>3</v>
+      </c>
+      <c r="C48" t="s">
+        <v>559</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48" t="s">
         <v>111</v>
-      </c>
-      <c r="B48" t="s">
-        <v>112</v>
-      </c>
-      <c r="C48">
-        <v>12.60253906</v>
-      </c>
-      <c r="D48">
-        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>112</v>
+      </c>
+      <c r="B49" t="s">
+        <v>3</v>
+      </c>
+      <c r="C49" t="s">
+        <v>560</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+      <c r="E49" t="s">
         <v>113</v>
-      </c>
-      <c r="B49" t="s">
-        <v>3</v>
-      </c>
-      <c r="C49">
-        <v>8</v>
-      </c>
-      <c r="D49">
-        <v>1</v>
-      </c>
-      <c r="E49" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>114</v>
+      </c>
+      <c r="B50" t="s">
+        <v>3</v>
+      </c>
+      <c r="C50" t="s">
+        <v>560</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50" t="s">
         <v>115</v>
-      </c>
-      <c r="B50" t="s">
-        <v>3</v>
-      </c>
-      <c r="C50">
-        <v>16</v>
-      </c>
-      <c r="D50">
-        <v>1</v>
-      </c>
-      <c r="E50" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>116</v>
+      </c>
+      <c r="B51" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" t="s">
+        <v>565</v>
+      </c>
+      <c r="D51">
+        <v>2</v>
+      </c>
+      <c r="E51" t="s">
         <v>117</v>
-      </c>
-      <c r="B51" t="s">
-        <v>3</v>
-      </c>
-      <c r="C51">
-        <v>16</v>
-      </c>
-      <c r="D51">
-        <v>1</v>
-      </c>
-      <c r="E51" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>118</v>
+      </c>
+      <c r="B52" t="s">
+        <v>3</v>
+      </c>
+      <c r="C52" t="s">
+        <v>560</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52" t="s">
         <v>119</v>
-      </c>
-      <c r="B52" t="s">
-        <v>18</v>
-      </c>
-      <c r="C52">
-        <v>127.9960938</v>
-      </c>
-      <c r="D52">
-        <v>2</v>
-      </c>
-      <c r="E52" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>120</v>
+      </c>
+      <c r="B53" t="s">
+        <v>58</v>
+      </c>
+      <c r="C53" t="s">
+        <v>564</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53" t="s">
         <v>121</v>
-      </c>
-      <c r="B53" t="s">
-        <v>3</v>
-      </c>
-      <c r="C53">
-        <v>16</v>
-      </c>
-      <c r="D53">
-        <v>1</v>
-      </c>
-      <c r="E53" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
-      </c>
-      <c r="C54">
-        <v>64</v>
+        <v>100</v>
+      </c>
+      <c r="C54" t="s">
+        <v>560</v>
       </c>
       <c r="D54">
         <v>1</v>
       </c>
       <c r="E54" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B55" t="s">
-        <v>123</v>
-      </c>
-      <c r="C55">
-        <v>9.704101563</v>
+        <v>3</v>
+      </c>
+      <c r="C55" t="s">
+        <v>559</v>
       </c>
       <c r="D55">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="E55" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>127</v>
+        <v>52</v>
       </c>
       <c r="B56" t="s">
-        <v>100</v>
-      </c>
-      <c r="C56">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="C56" t="s">
+        <v>563</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B57" t="s">
         <v>3</v>
       </c>
-      <c r="C57">
-        <v>8</v>
+      <c r="C57" t="s">
+        <v>560</v>
       </c>
       <c r="D57">
         <v>1</v>
       </c>
       <c r="E57" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>52</v>
+        <v>129</v>
       </c>
       <c r="B58" t="s">
-        <v>18</v>
-      </c>
-      <c r="C58">
-        <v>48</v>
+        <v>3</v>
+      </c>
+      <c r="C58" t="s">
+        <v>560</v>
       </c>
       <c r="D58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>131</v>
+      </c>
+      <c r="B59" t="s">
+        <v>3</v>
+      </c>
+      <c r="C59" t="s">
+        <v>559</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="E59" t="s">
         <v>132</v>
-      </c>
-      <c r="B59" t="s">
-        <v>112</v>
-      </c>
-      <c r="C59">
-        <v>19.50585938</v>
-      </c>
-      <c r="D59">
-        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
@@ -3689,10 +3663,10 @@
         <v>133</v>
       </c>
       <c r="B60" t="s">
-        <v>3</v>
-      </c>
-      <c r="C60">
-        <v>16</v>
+        <v>100</v>
+      </c>
+      <c r="C60" t="s">
+        <v>560</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -3706,10 +3680,10 @@
         <v>135</v>
       </c>
       <c r="B61" t="s">
-        <v>3</v>
-      </c>
-      <c r="C61">
-        <v>16</v>
+        <v>63</v>
+      </c>
+      <c r="C61" t="s">
+        <v>564</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -3723,10 +3697,10 @@
         <v>137</v>
       </c>
       <c r="B62" t="s">
-        <v>3</v>
-      </c>
-      <c r="C62">
-        <v>8</v>
+        <v>58</v>
+      </c>
+      <c r="C62" t="s">
+        <v>564</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -3740,13 +3714,13 @@
         <v>139</v>
       </c>
       <c r="B63" t="s">
-        <v>100</v>
-      </c>
-      <c r="C63">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="C63" t="s">
+        <v>564</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" t="s">
         <v>140</v>
@@ -3757,10 +3731,10 @@
         <v>141</v>
       </c>
       <c r="B64" t="s">
-        <v>63</v>
-      </c>
-      <c r="C64">
-        <v>63.951171879999997</v>
+        <v>3</v>
+      </c>
+      <c r="C64" t="s">
+        <v>561</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -3774,10 +3748,10 @@
         <v>143</v>
       </c>
       <c r="B65" t="s">
-        <v>58</v>
-      </c>
-      <c r="C65">
-        <v>64</v>
+        <v>12</v>
+      </c>
+      <c r="C65" t="s">
+        <v>561</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -3791,13 +3765,13 @@
         <v>145</v>
       </c>
       <c r="B66" t="s">
-        <v>18</v>
-      </c>
-      <c r="C66">
-        <v>63.998046879999997</v>
+        <v>3</v>
+      </c>
+      <c r="C66" t="s">
+        <v>560</v>
       </c>
       <c r="D66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" t="s">
         <v>146</v>
@@ -3810,8 +3784,8 @@
       <c r="B67" t="s">
         <v>3</v>
       </c>
-      <c r="C67">
-        <v>31.999023439999998</v>
+      <c r="C67" t="s">
+        <v>561</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -3822,33 +3796,33 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
+        <v>109</v>
+      </c>
+      <c r="B68" t="s">
         <v>149</v>
       </c>
-      <c r="B68" t="s">
-        <v>12</v>
-      </c>
-      <c r="C68">
-        <v>32</v>
+      <c r="C68" t="s">
+        <v>566</v>
       </c>
       <c r="D68">
-        <v>1</v>
-      </c>
-      <c r="E68" t="s">
-        <v>150</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>150</v>
+      </c>
+      <c r="B69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" t="s">
+        <v>564</v>
+      </c>
+      <c r="D69">
+        <v>2</v>
+      </c>
+      <c r="E69" t="s">
         <v>151</v>
-      </c>
-      <c r="B69" t="s">
-        <v>112</v>
-      </c>
-      <c r="C69">
-        <v>58.956054690000002</v>
-      </c>
-      <c r="D69">
-        <v>4</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -3858,8 +3832,8 @@
       <c r="B70" t="s">
         <v>3</v>
       </c>
-      <c r="C70">
-        <v>16</v>
+      <c r="C70" t="s">
+        <v>560</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -3873,13 +3847,16 @@
         <v>154</v>
       </c>
       <c r="B71" t="s">
+        <v>3</v>
+      </c>
+      <c r="C71" t="s">
+        <v>560</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="E71" t="s">
         <v>155</v>
-      </c>
-      <c r="C71">
-        <v>15.65136719</v>
-      </c>
-      <c r="D71">
-        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
@@ -3887,10 +3864,10 @@
         <v>156</v>
       </c>
       <c r="B72" t="s">
-        <v>3</v>
-      </c>
-      <c r="C72">
-        <v>31.999023439999998</v>
+        <v>63</v>
+      </c>
+      <c r="C72" t="s">
+        <v>564</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -3901,180 +3878,183 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>110</v>
+        <v>158</v>
       </c>
       <c r="B73" t="s">
-        <v>158</v>
-      </c>
-      <c r="C73">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="C73" t="s">
+        <v>563</v>
       </c>
       <c r="D73">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="E73" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B74" t="s">
-        <v>18</v>
-      </c>
-      <c r="C74">
-        <v>63.998046879999997</v>
+        <v>3</v>
+      </c>
+      <c r="C74" t="s">
+        <v>560</v>
       </c>
       <c r="D74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B75" t="s">
         <v>3</v>
       </c>
-      <c r="C75">
-        <v>16</v>
+      <c r="C75" t="s">
+        <v>559</v>
       </c>
       <c r="D75">
         <v>1</v>
       </c>
       <c r="E75" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B76" t="s">
         <v>3</v>
       </c>
-      <c r="C76">
-        <v>16</v>
+      <c r="C76" t="s">
+        <v>560</v>
       </c>
       <c r="D76">
         <v>1</v>
       </c>
       <c r="E76" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B77" t="s">
-        <v>63</v>
-      </c>
-      <c r="C77">
-        <v>63.951171879999997</v>
+        <v>18</v>
+      </c>
+      <c r="C77" t="s">
+        <v>564</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B78" t="s">
-        <v>18</v>
-      </c>
-      <c r="C78">
-        <v>48</v>
+        <v>3</v>
+      </c>
+      <c r="C78" t="s">
+        <v>560</v>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B79" t="s">
         <v>3</v>
       </c>
-      <c r="C79">
-        <v>16</v>
+      <c r="C79" t="s">
+        <v>560</v>
       </c>
       <c r="D79">
         <v>1</v>
       </c>
       <c r="E79" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B80" t="s">
         <v>3</v>
       </c>
-      <c r="C80">
-        <v>8</v>
+      <c r="C80" t="s">
+        <v>561</v>
       </c>
       <c r="D80">
         <v>1</v>
       </c>
       <c r="E80" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B81" t="s">
         <v>3</v>
       </c>
-      <c r="C81">
-        <v>16</v>
+      <c r="C81" t="s">
+        <v>560</v>
       </c>
       <c r="D81">
         <v>1</v>
       </c>
       <c r="E81" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B82" t="s">
-        <v>18</v>
-      </c>
-      <c r="C82">
-        <v>63.998046879999997</v>
+        <v>3</v>
+      </c>
+      <c r="C82" t="s">
+        <v>560</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E82" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>177</v>
+        <v>5</v>
       </c>
       <c r="B83" t="s">
         <v>3</v>
       </c>
-      <c r="C83">
-        <v>16</v>
+      <c r="C83" t="s">
+        <v>560</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -4085,3641 +4065,3301 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B84" t="s">
         <v>3</v>
       </c>
-      <c r="C84">
-        <v>16</v>
+      <c r="C84" t="s">
+        <v>560</v>
       </c>
       <c r="D84">
         <v>1</v>
       </c>
       <c r="E84" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B85" t="s">
-        <v>155</v>
-      </c>
-      <c r="C85">
-        <v>17.620117189999998</v>
+        <v>58</v>
+      </c>
+      <c r="C85" t="s">
+        <v>567</v>
       </c>
       <c r="D85">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="E85" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B86" t="s">
-        <v>3</v>
-      </c>
-      <c r="C86">
-        <v>32</v>
+        <v>185</v>
+      </c>
+      <c r="C86" t="s">
+        <v>560</v>
       </c>
       <c r="D86">
         <v>1</v>
       </c>
       <c r="E86" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B87" t="s">
         <v>3</v>
       </c>
-      <c r="C87">
-        <v>16</v>
+      <c r="C87" t="s">
+        <v>560</v>
       </c>
       <c r="D87">
         <v>1</v>
       </c>
       <c r="E87" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B88" t="s">
         <v>3</v>
       </c>
-      <c r="C88">
-        <v>16</v>
+      <c r="C88" t="s">
+        <v>560</v>
       </c>
       <c r="D88">
         <v>1</v>
       </c>
       <c r="E88" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>5</v>
+        <v>191</v>
       </c>
       <c r="B89" t="s">
         <v>3</v>
       </c>
-      <c r="C89">
-        <v>16</v>
+      <c r="C89" t="s">
+        <v>560</v>
       </c>
       <c r="D89">
         <v>1</v>
       </c>
       <c r="E89" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B90" t="s">
-        <v>3</v>
-      </c>
-      <c r="C90">
-        <v>16</v>
+        <v>58</v>
+      </c>
+      <c r="C90" t="s">
+        <v>561</v>
       </c>
       <c r="D90">
         <v>1</v>
       </c>
       <c r="E90" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B91" t="s">
-        <v>58</v>
-      </c>
-      <c r="C91">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="C91" t="s">
+        <v>559</v>
       </c>
       <c r="D91">
         <v>1</v>
       </c>
       <c r="E91" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B92" t="s">
-        <v>195</v>
-      </c>
-      <c r="C92">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="C92" t="s">
+        <v>564</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B93" t="s">
-        <v>3</v>
-      </c>
-      <c r="C93">
-        <v>16</v>
+        <v>100</v>
+      </c>
+      <c r="C93" t="s">
+        <v>560</v>
       </c>
       <c r="D93">
         <v>1</v>
       </c>
       <c r="E93" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B94" t="s">
         <v>3</v>
       </c>
-      <c r="C94">
-        <v>16</v>
+      <c r="C94" t="s">
+        <v>559</v>
       </c>
       <c r="D94">
         <v>1</v>
       </c>
       <c r="E94" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B95" t="s">
-        <v>3</v>
-      </c>
-      <c r="C95">
-        <v>16</v>
+        <v>63</v>
+      </c>
+      <c r="C95" t="s">
+        <v>564</v>
       </c>
       <c r="D95">
         <v>1</v>
       </c>
       <c r="E95" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B96" t="s">
-        <v>58</v>
-      </c>
-      <c r="C96">
-        <v>31.95117188</v>
+        <v>3</v>
+      </c>
+      <c r="C96" t="s">
+        <v>560</v>
       </c>
       <c r="D96">
         <v>1</v>
       </c>
       <c r="E96" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B97" t="s">
-        <v>112</v>
-      </c>
-      <c r="C97">
-        <v>58.956054690000002</v>
+        <v>3</v>
+      </c>
+      <c r="C97" t="s">
+        <v>559</v>
       </c>
       <c r="D97">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="E97" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B98" t="s">
-        <v>3</v>
-      </c>
-      <c r="C98">
-        <v>8</v>
+        <v>18</v>
+      </c>
+      <c r="C98" t="s">
+        <v>564</v>
       </c>
       <c r="D98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E98" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B99" t="s">
         <v>18</v>
       </c>
-      <c r="C99">
-        <v>63.998046879999997</v>
+      <c r="C99" t="s">
+        <v>559</v>
       </c>
       <c r="D99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E99" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
-      </c>
-      <c r="C100">
-        <v>16</v>
+        <v>3</v>
+      </c>
+      <c r="C100" t="s">
+        <v>560</v>
       </c>
       <c r="D100">
         <v>1</v>
       </c>
       <c r="E100" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B101" t="s">
-        <v>155</v>
-      </c>
-      <c r="C101">
-        <v>15.65136719</v>
+        <v>3</v>
+      </c>
+      <c r="C101" t="s">
+        <v>559</v>
       </c>
       <c r="D101">
         <v>1</v>
+      </c>
+      <c r="E101" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B102" t="s">
-        <v>3</v>
-      </c>
-      <c r="C102">
-        <v>8</v>
+        <v>18</v>
+      </c>
+      <c r="C102" t="s">
+        <v>564</v>
       </c>
       <c r="D102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E102" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B103" t="s">
-        <v>63</v>
-      </c>
-      <c r="C103">
-        <v>63.951171879999997</v>
+        <v>18</v>
+      </c>
+      <c r="C103" t="s">
+        <v>564</v>
       </c>
       <c r="D103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B104" t="s">
         <v>3</v>
       </c>
-      <c r="C104">
-        <v>16</v>
+      <c r="C104" t="s">
+        <v>560</v>
       </c>
       <c r="D104">
         <v>1</v>
       </c>
       <c r="E104" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B105" t="s">
         <v>3</v>
       </c>
-      <c r="C105">
-        <v>8</v>
+      <c r="C105" t="s">
+        <v>561</v>
       </c>
       <c r="D105">
         <v>1</v>
       </c>
       <c r="E105" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B106" t="s">
-        <v>18</v>
-      </c>
-      <c r="C106">
-        <v>63.998046879999997</v>
+        <v>100</v>
+      </c>
+      <c r="C106" t="s">
+        <v>560</v>
       </c>
       <c r="D106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E106" t="s">
-        <v>207</v>
+        <v>115</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>226</v>
+        <v>179</v>
       </c>
       <c r="B107" t="s">
-        <v>18</v>
-      </c>
-      <c r="C107">
+        <v>149</v>
+      </c>
+      <c r="C107" t="s">
+        <v>568</v>
+      </c>
+      <c r="D107">
         <v>8</v>
-      </c>
-      <c r="D107">
-        <v>1</v>
-      </c>
-      <c r="E107" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B108" t="s">
         <v>3</v>
       </c>
-      <c r="C108">
-        <v>16</v>
+      <c r="C108" t="s">
+        <v>560</v>
       </c>
       <c r="D108">
         <v>1</v>
       </c>
       <c r="E108" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B109" t="s">
-        <v>3</v>
-      </c>
-      <c r="C109">
-        <v>8</v>
+        <v>58</v>
+      </c>
+      <c r="C109" t="s">
+        <v>564</v>
       </c>
       <c r="D109">
         <v>1</v>
       </c>
       <c r="E109" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B110" t="s">
-        <v>18</v>
-      </c>
-      <c r="C110">
-        <v>63.998046879999997</v>
+        <v>3</v>
+      </c>
+      <c r="C110" t="s">
+        <v>560</v>
       </c>
       <c r="D110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E110" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B111" t="s">
-        <v>18</v>
-      </c>
-      <c r="C111">
-        <v>64</v>
+        <v>3</v>
+      </c>
+      <c r="C111" t="s">
+        <v>560</v>
       </c>
       <c r="D111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E111" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B112" t="s">
-        <v>3</v>
-      </c>
-      <c r="C112">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="C112" t="s">
+        <v>563</v>
       </c>
       <c r="D112">
         <v>1</v>
       </c>
       <c r="E112" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B113" t="s">
         <v>3</v>
       </c>
-      <c r="C113">
-        <v>31.999023439999998</v>
+      <c r="C113" t="s">
+        <v>560</v>
       </c>
       <c r="D113">
         <v>1</v>
       </c>
       <c r="E113" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B114" t="s">
-        <v>100</v>
-      </c>
-      <c r="C114">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="C114" t="s">
+        <v>564</v>
       </c>
       <c r="D114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E114" t="s">
-        <v>118</v>
+        <v>242</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>189</v>
+        <v>243</v>
       </c>
       <c r="B115" t="s">
-        <v>158</v>
-      </c>
-      <c r="C115">
-        <v>28</v>
+        <v>3</v>
+      </c>
+      <c r="C115" t="s">
+        <v>559</v>
       </c>
       <c r="D115">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="E115" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B116" t="s">
-        <v>3</v>
-      </c>
-      <c r="C116">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="C116" t="s">
+        <v>565</v>
       </c>
       <c r="D116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E116" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B117" t="s">
-        <v>58</v>
-      </c>
-      <c r="C117">
-        <v>63.951171879999997</v>
+        <v>18</v>
+      </c>
+      <c r="C117" t="s">
+        <v>564</v>
       </c>
       <c r="D117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E117" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>245</v>
+        <v>201</v>
       </c>
       <c r="B118" t="s">
         <v>3</v>
       </c>
-      <c r="C118">
-        <v>16</v>
+      <c r="C118" t="s">
+        <v>560</v>
       </c>
       <c r="D118">
         <v>1</v>
       </c>
       <c r="E118" t="s">
-        <v>246</v>
+        <v>202</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B119" t="s">
-        <v>3</v>
-      </c>
-      <c r="C119">
-        <v>16</v>
+        <v>12</v>
+      </c>
+      <c r="C119" t="s">
+        <v>564</v>
       </c>
       <c r="D119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E119" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B120" t="s">
-        <v>18</v>
-      </c>
-      <c r="C120">
-        <v>48</v>
+        <v>58</v>
+      </c>
+      <c r="C120" t="s">
+        <v>559</v>
       </c>
       <c r="D120">
         <v>1</v>
       </c>
       <c r="E120" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B121" t="s">
-        <v>3</v>
-      </c>
-      <c r="C121">
-        <v>16</v>
+        <v>63</v>
+      </c>
+      <c r="C121" t="s">
+        <v>560</v>
       </c>
       <c r="D121">
         <v>1</v>
       </c>
       <c r="E121" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B122" t="s">
-        <v>112</v>
-      </c>
-      <c r="C122">
-        <v>21.47851563</v>
+        <v>18</v>
+      </c>
+      <c r="C122" t="s">
+        <v>561</v>
       </c>
       <c r="D122">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="E122" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B123" t="s">
-        <v>18</v>
-      </c>
-      <c r="C123">
-        <v>63.998046879999997</v>
+        <v>3</v>
+      </c>
+      <c r="C123" t="s">
+        <v>560</v>
       </c>
       <c r="D123">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E123" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B124" t="s">
         <v>3</v>
       </c>
-      <c r="C124">
-        <v>8</v>
+      <c r="C124" t="s">
+        <v>559</v>
       </c>
       <c r="D124">
         <v>1</v>
       </c>
       <c r="E124" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B125" t="s">
         <v>18</v>
       </c>
-      <c r="C125">
-        <v>127.9960938</v>
+      <c r="C125" t="s">
+        <v>564</v>
       </c>
       <c r="D125">
         <v>2</v>
       </c>
       <c r="E125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B126" t="s">
-        <v>18</v>
-      </c>
-      <c r="C126">
-        <v>63.998046879999997</v>
+        <v>3</v>
+      </c>
+      <c r="C126" t="s">
+        <v>559</v>
       </c>
       <c r="D126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E126" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>212</v>
+        <v>265</v>
       </c>
       <c r="B127" t="s">
         <v>3</v>
       </c>
-      <c r="C127">
-        <v>16</v>
+      <c r="C127" t="s">
+        <v>560</v>
       </c>
       <c r="D127">
         <v>1</v>
       </c>
       <c r="E127" t="s">
-        <v>213</v>
+        <v>266</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B128" t="s">
         <v>12</v>
       </c>
-      <c r="C128">
-        <v>64</v>
+      <c r="C128" t="s">
+        <v>561</v>
       </c>
       <c r="D128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E128" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B129" t="s">
-        <v>112</v>
-      </c>
-      <c r="C129">
-        <v>15.56054688</v>
+        <v>3</v>
+      </c>
+      <c r="C129" t="s">
+        <v>569</v>
       </c>
       <c r="D129">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="E129" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B130" t="s">
-        <v>58</v>
-      </c>
-      <c r="C130">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="C130" t="s">
+        <v>560</v>
       </c>
       <c r="D130">
         <v>1</v>
       </c>
       <c r="E130" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B131" t="s">
-        <v>63</v>
-      </c>
-      <c r="C131">
-        <v>15.95117188</v>
+        <v>58</v>
+      </c>
+      <c r="C131" t="s">
+        <v>561</v>
       </c>
       <c r="D131">
         <v>1</v>
       </c>
       <c r="E131" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B132" t="s">
-        <v>18</v>
-      </c>
-      <c r="C132">
-        <v>31.999023439999998</v>
+        <v>3</v>
+      </c>
+      <c r="C132" t="s">
+        <v>560</v>
       </c>
       <c r="D132">
         <v>1</v>
       </c>
       <c r="E132" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B133" t="s">
         <v>3</v>
       </c>
-      <c r="C133">
-        <v>16</v>
+      <c r="C133" t="s">
+        <v>560</v>
       </c>
       <c r="D133">
         <v>1</v>
       </c>
       <c r="E133" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B134" t="s">
-        <v>3</v>
-      </c>
-      <c r="C134">
-        <v>8</v>
+        <v>280</v>
+      </c>
+      <c r="C134" t="s">
+        <v>561</v>
       </c>
       <c r="D134">
         <v>1</v>
       </c>
       <c r="E134" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="B135" t="s">
-        <v>18</v>
-      </c>
-      <c r="C135">
-        <v>63.998046879999997</v>
+        <v>3</v>
+      </c>
+      <c r="C135" t="s">
+        <v>560</v>
       </c>
       <c r="D135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E135" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="B136" t="s">
         <v>3</v>
       </c>
-      <c r="C136">
-        <v>8</v>
+      <c r="C136" t="s">
+        <v>560</v>
       </c>
       <c r="D136">
         <v>1</v>
       </c>
       <c r="E136" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="B137" t="s">
         <v>3</v>
       </c>
-      <c r="C137">
-        <v>16</v>
+      <c r="C137" t="s">
+        <v>560</v>
       </c>
       <c r="D137">
         <v>1</v>
       </c>
       <c r="E137" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="B138" t="s">
-        <v>12</v>
-      </c>
-      <c r="C138">
-        <v>32</v>
+        <v>3</v>
+      </c>
+      <c r="C138" t="s">
+        <v>559</v>
       </c>
       <c r="D138">
         <v>1</v>
       </c>
       <c r="E138" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B139" t="s">
-        <v>3</v>
-      </c>
-      <c r="C139">
-        <v>512</v>
+        <v>18</v>
+      </c>
+      <c r="C139" t="s">
+        <v>564</v>
       </c>
       <c r="D139">
         <v>2</v>
       </c>
       <c r="E139" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="B140" t="s">
-        <v>3</v>
-      </c>
-      <c r="C140">
-        <v>16</v>
+        <v>63</v>
+      </c>
+      <c r="C140" t="s">
+        <v>559</v>
       </c>
       <c r="D140">
         <v>1</v>
       </c>
       <c r="E140" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="B141" t="s">
-        <v>58</v>
-      </c>
-      <c r="C141">
-        <v>31.95117188</v>
+        <v>3</v>
+      </c>
+      <c r="C141" t="s">
+        <v>561</v>
       </c>
       <c r="D141">
         <v>1</v>
       </c>
       <c r="E141" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="B142" t="s">
         <v>3</v>
       </c>
-      <c r="C142">
-        <v>16</v>
+      <c r="C142" t="s">
+        <v>561</v>
       </c>
       <c r="D142">
         <v>1</v>
       </c>
       <c r="E142" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="B143" t="s">
-        <v>3</v>
-      </c>
-      <c r="C143">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="C143" t="s">
+        <v>564</v>
       </c>
       <c r="D143">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E143" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="B144" t="s">
-        <v>294</v>
-      </c>
-      <c r="C144">
-        <v>31.95117188</v>
+        <v>3</v>
+      </c>
+      <c r="C144" t="s">
+        <v>560</v>
       </c>
       <c r="D144">
         <v>1</v>
       </c>
       <c r="E144" t="s">
-        <v>295</v>
+        <v>165</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B145" t="s">
-        <v>3</v>
-      </c>
-      <c r="C145">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="C145" t="s">
+        <v>564</v>
       </c>
       <c r="D145">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E145" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B146" t="s">
         <v>3</v>
       </c>
-      <c r="C146">
-        <v>16</v>
+      <c r="C146" t="s">
+        <v>560</v>
       </c>
       <c r="D146">
         <v>1</v>
       </c>
       <c r="E146" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B147" t="s">
         <v>3</v>
       </c>
-      <c r="C147">
-        <v>16</v>
+      <c r="C147" t="s">
+        <v>559</v>
       </c>
       <c r="D147">
         <v>1</v>
       </c>
       <c r="E147" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B148" t="s">
         <v>3</v>
       </c>
-      <c r="C148">
-        <v>8</v>
+      <c r="C148" t="s">
+        <v>560</v>
       </c>
       <c r="D148">
         <v>1</v>
       </c>
       <c r="E148" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B149" t="s">
-        <v>18</v>
-      </c>
-      <c r="C149">
-        <v>63.998046879999997</v>
+        <v>63</v>
+      </c>
+      <c r="C149" t="s">
+        <v>564</v>
       </c>
       <c r="D149">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E149" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B150" t="s">
         <v>63</v>
       </c>
-      <c r="C150">
-        <v>7.951171875</v>
+      <c r="C150" t="s">
+        <v>560</v>
       </c>
       <c r="D150">
         <v>1</v>
       </c>
       <c r="E150" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B151" t="s">
         <v>3</v>
       </c>
-      <c r="C151">
-        <v>31.999023439999998</v>
+      <c r="C151" t="s">
+        <v>560</v>
       </c>
       <c r="D151">
         <v>1</v>
       </c>
       <c r="E151" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B152" t="s">
-        <v>112</v>
-      </c>
-      <c r="C152">
-        <v>2.802734375</v>
+        <v>18</v>
+      </c>
+      <c r="C152" t="s">
+        <v>570</v>
       </c>
       <c r="D152">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="E152" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B153" t="s">
-        <v>3</v>
-      </c>
-      <c r="C153">
-        <v>31.999023439999998</v>
+        <v>18</v>
+      </c>
+      <c r="C153" t="s">
+        <v>559</v>
       </c>
       <c r="D153">
         <v>1</v>
       </c>
       <c r="E153" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B154" t="s">
         <v>18</v>
       </c>
-      <c r="C154">
-        <v>64</v>
+      <c r="C154" t="s">
+        <v>565</v>
       </c>
       <c r="D154">
         <v>2</v>
       </c>
       <c r="E154" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B155" t="s">
-        <v>112</v>
-      </c>
-      <c r="C155">
-        <v>15.56054688</v>
+        <v>18</v>
+      </c>
+      <c r="C155" t="s">
+        <v>565</v>
       </c>
       <c r="D155">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="E155" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B156" t="s">
-        <v>3</v>
-      </c>
-      <c r="C156">
-        <v>16</v>
+        <v>63</v>
+      </c>
+      <c r="C156" t="s">
+        <v>560</v>
       </c>
       <c r="D156">
         <v>1</v>
       </c>
       <c r="E156" t="s">
-        <v>174</v>
+        <v>324</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="B157" t="s">
-        <v>18</v>
-      </c>
-      <c r="C157">
-        <v>63.998046879999997</v>
+        <v>3</v>
+      </c>
+      <c r="C157" t="s">
+        <v>560</v>
       </c>
       <c r="D157">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E157" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B158" t="s">
-        <v>112</v>
-      </c>
-      <c r="C158">
-        <v>56.983398440000002</v>
+        <v>12</v>
+      </c>
+      <c r="C158" t="s">
+        <v>561</v>
       </c>
       <c r="D158">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="E158" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="B159" t="s">
         <v>3</v>
       </c>
-      <c r="C159">
-        <v>16</v>
+      <c r="C159" t="s">
+        <v>559</v>
       </c>
       <c r="D159">
         <v>1</v>
       </c>
       <c r="E159" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="B160" t="s">
         <v>3</v>
       </c>
-      <c r="C160">
-        <v>8</v>
+      <c r="C160" t="s">
+        <v>560</v>
       </c>
       <c r="D160">
         <v>1</v>
       </c>
       <c r="E160" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="B161" t="s">
-        <v>112</v>
-      </c>
-      <c r="C161">
-        <v>9.643554688</v>
+        <v>3</v>
+      </c>
+      <c r="C161" t="s">
+        <v>560</v>
       </c>
       <c r="D161">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="E161" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="B162" t="s">
         <v>3</v>
       </c>
-      <c r="C162">
-        <v>16</v>
+      <c r="C162" t="s">
+        <v>561</v>
       </c>
       <c r="D162">
         <v>1</v>
       </c>
       <c r="E162" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="B163" t="s">
-        <v>63</v>
-      </c>
-      <c r="C163">
-        <v>63.951171879999997</v>
+        <v>3</v>
+      </c>
+      <c r="C163" t="s">
+        <v>560</v>
       </c>
       <c r="D163">
         <v>1</v>
       </c>
       <c r="E163" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="B164" t="s">
-        <v>63</v>
-      </c>
-      <c r="C164">
-        <v>15.95117188</v>
+        <v>3</v>
+      </c>
+      <c r="C164" t="s">
+        <v>560</v>
       </c>
       <c r="D164">
         <v>1</v>
       </c>
       <c r="E164" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="B165" t="s">
         <v>3</v>
       </c>
-      <c r="C165">
-        <v>16</v>
+      <c r="C165" t="s">
+        <v>561</v>
       </c>
       <c r="D165">
         <v>1</v>
       </c>
       <c r="E165" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="B166" t="s">
-        <v>112</v>
-      </c>
-      <c r="C166">
-        <v>46.134765629999997</v>
+        <v>3</v>
+      </c>
+      <c r="C166" t="s">
+        <v>560</v>
       </c>
       <c r="D166">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="E166" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="B167" t="s">
         <v>18</v>
       </c>
-      <c r="C167">
-        <v>49</v>
+      <c r="C167" t="s">
+        <v>564</v>
       </c>
       <c r="D167">
         <v>2</v>
       </c>
       <c r="E167" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="B168" t="s">
         <v>18</v>
       </c>
-      <c r="C168">
-        <v>8</v>
+      <c r="C168" t="s">
+        <v>564</v>
       </c>
       <c r="D168">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E168" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="B169" t="s">
-        <v>18</v>
-      </c>
-      <c r="C169">
-        <v>127.9960938</v>
+        <v>100</v>
+      </c>
+      <c r="C169" t="s">
+        <v>560</v>
       </c>
       <c r="D169">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E169" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="B170" t="s">
-        <v>18</v>
-      </c>
-      <c r="C170">
-        <v>127.9960938</v>
+        <v>63</v>
+      </c>
+      <c r="C170" t="s">
+        <v>564</v>
       </c>
       <c r="D170">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E170" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="B171" t="s">
-        <v>63</v>
-      </c>
-      <c r="C171">
-        <v>15.95117188</v>
+        <v>3</v>
+      </c>
+      <c r="C171" t="s">
+        <v>560</v>
       </c>
       <c r="D171">
         <v>1</v>
       </c>
       <c r="E171" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="B172" t="s">
         <v>3</v>
       </c>
-      <c r="C172">
-        <v>16</v>
+      <c r="C172" t="s">
+        <v>559</v>
       </c>
       <c r="D172">
         <v>1</v>
       </c>
       <c r="E172" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="B173" t="s">
-        <v>12</v>
-      </c>
-      <c r="C173">
-        <v>32</v>
+        <v>18</v>
+      </c>
+      <c r="C173" t="s">
+        <v>559</v>
       </c>
       <c r="D173">
         <v>1</v>
       </c>
       <c r="E173" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="B174" t="s">
-        <v>3</v>
-      </c>
-      <c r="C174">
-        <v>8</v>
+        <v>18</v>
+      </c>
+      <c r="C174" t="s">
+        <v>571</v>
       </c>
       <c r="D174">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E174" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="B175" t="s">
         <v>3</v>
       </c>
-      <c r="C175">
-        <v>16</v>
+      <c r="C175" t="s">
+        <v>560</v>
       </c>
       <c r="D175">
         <v>1</v>
       </c>
       <c r="E175" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="B176" t="s">
-        <v>3</v>
-      </c>
-      <c r="C176">
-        <v>16</v>
+        <v>58</v>
+      </c>
+      <c r="C176" t="s">
+        <v>559</v>
       </c>
       <c r="D176">
         <v>1</v>
       </c>
       <c r="E176" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="B177" t="s">
-        <v>3</v>
-      </c>
-      <c r="C177">
-        <v>31.999023439999998</v>
+        <v>18</v>
+      </c>
+      <c r="C177" t="s">
+        <v>564</v>
       </c>
       <c r="D177">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E177" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="B178" t="s">
         <v>3</v>
       </c>
-      <c r="C178">
-        <v>16</v>
+      <c r="C178" t="s">
+        <v>560</v>
       </c>
       <c r="D178">
         <v>1</v>
       </c>
       <c r="E178" t="s">
-        <v>357</v>
+        <v>165</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="B179" t="s">
-        <v>103</v>
-      </c>
-      <c r="C179">
-        <v>4.770507813</v>
+        <v>3</v>
+      </c>
+      <c r="C179" t="s">
+        <v>560</v>
       </c>
       <c r="D179">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="E179" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="B180" t="s">
-        <v>3</v>
-      </c>
-      <c r="C180">
-        <v>16</v>
+        <v>12</v>
+      </c>
+      <c r="C180" t="s">
+        <v>561</v>
       </c>
       <c r="D180">
         <v>1</v>
       </c>
       <c r="E180" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="B181" t="s">
-        <v>3</v>
-      </c>
-      <c r="C181">
-        <v>32</v>
+        <v>18</v>
+      </c>
+      <c r="C181" t="s">
+        <v>564</v>
       </c>
       <c r="D181">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E181" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="B182" t="s">
         <v>3</v>
       </c>
-      <c r="C182">
-        <v>16</v>
+      <c r="C182" t="s">
+        <v>560</v>
       </c>
       <c r="D182">
         <v>1</v>
       </c>
       <c r="E182" t="s">
-        <v>134</v>
+        <v>375</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="B183" t="s">
-        <v>18</v>
-      </c>
-      <c r="C183">
-        <v>63.998046879999997</v>
+        <v>280</v>
+      </c>
+      <c r="C183" t="s">
+        <v>560</v>
       </c>
       <c r="D183">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E183" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="B184" t="s">
-        <v>18</v>
-      </c>
-      <c r="C184">
-        <v>63.998046879999997</v>
+        <v>3</v>
+      </c>
+      <c r="C184" t="s">
+        <v>560</v>
       </c>
       <c r="D184">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E184" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="B185" t="s">
-        <v>100</v>
-      </c>
-      <c r="C185">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="C185" t="s">
+        <v>560</v>
       </c>
       <c r="D185">
         <v>1</v>
       </c>
       <c r="E185" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="B186" t="s">
-        <v>112</v>
-      </c>
-      <c r="C186">
-        <v>9.643554688</v>
+        <v>18</v>
+      </c>
+      <c r="C186" t="s">
+        <v>565</v>
       </c>
       <c r="D186">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="E186" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="B187" t="s">
-        <v>63</v>
-      </c>
-      <c r="C187">
-        <v>63.951171879999997</v>
+        <v>3</v>
+      </c>
+      <c r="C187" t="s">
+        <v>559</v>
       </c>
       <c r="D187">
         <v>1</v>
       </c>
       <c r="E187" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="B188" t="s">
-        <v>3</v>
-      </c>
-      <c r="C188">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="C188" t="s">
+        <v>564</v>
       </c>
       <c r="D188">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E188" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="B189" t="s">
-        <v>3</v>
-      </c>
-      <c r="C189">
-        <v>8</v>
+        <v>100</v>
+      </c>
+      <c r="C189" t="s">
+        <v>560</v>
       </c>
       <c r="D189">
         <v>1</v>
       </c>
       <c r="E189" t="s">
-        <v>376</v>
+        <v>349</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="B190" t="s">
         <v>18</v>
       </c>
-      <c r="C190">
-        <v>8</v>
+      <c r="C190" t="s">
+        <v>565</v>
       </c>
       <c r="D190">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E190" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="B191" t="s">
-        <v>18</v>
-      </c>
-      <c r="C191">
-        <v>80</v>
+        <v>3</v>
+      </c>
+      <c r="C191" t="s">
+        <v>560</v>
       </c>
       <c r="D191">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E191" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="B192" t="s">
-        <v>112</v>
-      </c>
-      <c r="C192">
-        <v>12.60253906</v>
+        <v>3</v>
+      </c>
+      <c r="C192" t="s">
+        <v>559</v>
       </c>
       <c r="D192">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="E192" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="B193" t="s">
-        <v>3</v>
-      </c>
-      <c r="C193">
-        <v>16</v>
+        <v>63</v>
+      </c>
+      <c r="C193" t="s">
+        <v>564</v>
       </c>
       <c r="D193">
         <v>1</v>
       </c>
       <c r="E193" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="B194" t="s">
         <v>58</v>
       </c>
-      <c r="C194">
-        <v>8</v>
+      <c r="C194" t="s">
+        <v>564</v>
       </c>
       <c r="D194">
         <v>1</v>
       </c>
       <c r="E194" t="s">
-        <v>386</v>
+        <v>121</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="B195" t="s">
-        <v>18</v>
-      </c>
-      <c r="C195">
-        <v>63.998046879999997</v>
+        <v>3</v>
+      </c>
+      <c r="C195" t="s">
+        <v>569</v>
       </c>
       <c r="D195">
         <v>2</v>
       </c>
       <c r="E195" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="B196" t="s">
         <v>3</v>
       </c>
-      <c r="C196">
-        <v>16</v>
+      <c r="C196" t="s">
+        <v>560</v>
       </c>
       <c r="D196">
         <v>1</v>
       </c>
       <c r="E196" t="s">
-        <v>174</v>
+        <v>401</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="B197" t="s">
         <v>3</v>
       </c>
-      <c r="C197">
-        <v>16</v>
+      <c r="C197" t="s">
+        <v>560</v>
       </c>
       <c r="D197">
         <v>1</v>
       </c>
       <c r="E197" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="B198" t="s">
-        <v>12</v>
-      </c>
-      <c r="C198">
-        <v>32</v>
+        <v>149</v>
+      </c>
+      <c r="C198" t="s">
+        <v>559</v>
       </c>
       <c r="D198">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E198" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="B199" t="s">
-        <v>18</v>
-      </c>
-      <c r="C199">
-        <v>63.998046879999997</v>
+        <v>100</v>
+      </c>
+      <c r="C199" t="s">
+        <v>560</v>
       </c>
       <c r="D199">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E199" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="B200" t="s">
         <v>3</v>
       </c>
-      <c r="C200">
-        <v>16</v>
+      <c r="C200" t="s">
+        <v>559</v>
       </c>
       <c r="D200">
         <v>1</v>
       </c>
       <c r="E200" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="B201" t="s">
-        <v>294</v>
-      </c>
-      <c r="C201">
-        <v>15.95117188</v>
+        <v>18</v>
+      </c>
+      <c r="C201" t="s">
+        <v>564</v>
       </c>
       <c r="D201">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E201" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="B202" t="s">
-        <v>3</v>
-      </c>
-      <c r="C202">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="C202" t="s">
+        <v>564</v>
       </c>
       <c r="D202">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E202" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>402</v>
+        <v>35</v>
       </c>
       <c r="B203" t="s">
         <v>18</v>
       </c>
-      <c r="C203">
-        <v>16</v>
+      <c r="C203" t="s">
+        <v>563</v>
       </c>
       <c r="D203">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E203" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="B204" t="s">
         <v>18</v>
       </c>
-      <c r="C204">
-        <v>127.9960938</v>
+      <c r="C204" t="s">
+        <v>563</v>
       </c>
       <c r="D204">
         <v>2</v>
       </c>
       <c r="E204" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="B205" t="s">
-        <v>3</v>
-      </c>
-      <c r="C205">
-        <v>8</v>
+        <v>18</v>
+      </c>
+      <c r="C205" t="s">
+        <v>564</v>
       </c>
       <c r="D205">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E205" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="B206" t="s">
         <v>18</v>
       </c>
-      <c r="C206">
-        <v>63.998046879999997</v>
+      <c r="C206" t="s">
+        <v>563</v>
       </c>
       <c r="D206">
         <v>2</v>
       </c>
       <c r="E206" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>410</v>
+        <v>49</v>
       </c>
       <c r="B207" t="s">
-        <v>100</v>
-      </c>
-      <c r="C207">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="C207" t="s">
+        <v>563</v>
       </c>
       <c r="D207">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E207" t="s">
-        <v>369</v>
+        <v>421</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="B208" t="s">
         <v>18</v>
       </c>
-      <c r="C208">
-        <v>127.9960938</v>
+      <c r="C208" t="s">
+        <v>564</v>
       </c>
       <c r="D208">
         <v>2</v>
       </c>
       <c r="E208" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="B209" t="s">
-        <v>3</v>
-      </c>
-      <c r="C209">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="C209" t="s">
+        <v>563</v>
       </c>
       <c r="D209">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E209" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="B210" t="s">
-        <v>3</v>
-      </c>
-      <c r="C210">
-        <v>8</v>
+        <v>18</v>
+      </c>
+      <c r="C210" t="s">
+        <v>563</v>
       </c>
       <c r="D210">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E210" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="B211" t="s">
-        <v>63</v>
-      </c>
-      <c r="C211">
-        <v>63.951171879999997</v>
+        <v>18</v>
+      </c>
+      <c r="C211" t="s">
+        <v>564</v>
       </c>
       <c r="D211">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E211" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>419</v>
+        <v>88</v>
       </c>
       <c r="B212" t="s">
-        <v>58</v>
-      </c>
-      <c r="C212">
-        <v>64</v>
+        <v>18</v>
+      </c>
+      <c r="C212" t="s">
+        <v>563</v>
       </c>
       <c r="D212">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E212" t="s">
-        <v>125</v>
+        <v>430</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="B213" t="s">
-        <v>3</v>
-      </c>
-      <c r="C213">
-        <v>512</v>
+        <v>18</v>
+      </c>
+      <c r="C213" t="s">
+        <v>564</v>
       </c>
       <c r="D213">
         <v>2</v>
       </c>
       <c r="E213" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="B214" t="s">
-        <v>3</v>
-      </c>
-      <c r="C214">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="C214" t="s">
+        <v>564</v>
       </c>
       <c r="D214">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E214" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>424</v>
+        <v>97</v>
       </c>
       <c r="B215" t="s">
-        <v>123</v>
-      </c>
-      <c r="C215">
-        <v>11.42285156</v>
+        <v>18</v>
+      </c>
+      <c r="C215" t="s">
+        <v>563</v>
       </c>
       <c r="D215">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="E215" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>425</v>
+        <v>81</v>
       </c>
       <c r="B216" t="s">
-        <v>3</v>
-      </c>
-      <c r="C216">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="C216" t="s">
+        <v>563</v>
       </c>
       <c r="D216">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E216" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="B217" t="s">
-        <v>158</v>
-      </c>
-      <c r="C217">
-        <v>7.787109375</v>
+        <v>18</v>
+      </c>
+      <c r="C217" t="s">
+        <v>564</v>
       </c>
       <c r="D217">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E217" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>429</v>
+        <v>356</v>
       </c>
       <c r="B218" t="s">
-        <v>100</v>
-      </c>
-      <c r="C218">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="C218" t="s">
+        <v>563</v>
       </c>
       <c r="D218">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E218" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="B219" t="s">
-        <v>112</v>
-      </c>
-      <c r="C219">
-        <v>9.643554688</v>
+        <v>18</v>
+      </c>
+      <c r="C219" t="s">
+        <v>563</v>
       </c>
       <c r="D219">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="E219" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="B220" t="s">
-        <v>155</v>
-      </c>
-      <c r="C220">
-        <v>31.243164060000002</v>
+        <v>18</v>
+      </c>
+      <c r="C220" t="s">
+        <v>564</v>
       </c>
       <c r="D220">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="E220" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="B221" t="s">
-        <v>3</v>
-      </c>
-      <c r="C221">
-        <v>8</v>
+        <v>18</v>
+      </c>
+      <c r="C221" t="s">
+        <v>563</v>
       </c>
       <c r="D221">
         <v>1</v>
       </c>
       <c r="E221" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="B222" t="s">
         <v>18</v>
       </c>
-      <c r="C222">
-        <v>63.998046879999997</v>
+      <c r="C222" t="s">
+        <v>563</v>
       </c>
       <c r="D222">
         <v>2</v>
       </c>
       <c r="E222" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>437</v>
+        <v>195</v>
       </c>
       <c r="B223" t="s">
-        <v>112</v>
-      </c>
-      <c r="C223">
-        <v>58.956054690000002</v>
+        <v>18</v>
+      </c>
+      <c r="C223" t="s">
+        <v>563</v>
       </c>
       <c r="D223">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="E223" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="B224" t="s">
         <v>18</v>
       </c>
-      <c r="C224">
-        <v>64</v>
+      <c r="C224" t="s">
+        <v>565</v>
       </c>
       <c r="D224">
         <v>2</v>
       </c>
       <c r="E224" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>35</v>
+        <v>451</v>
       </c>
       <c r="B225" t="s">
         <v>18</v>
       </c>
-      <c r="C225">
-        <v>48</v>
+      <c r="C225" t="s">
+        <v>564</v>
       </c>
       <c r="D225">
         <v>2</v>
       </c>
       <c r="E225" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="B226" t="s">
         <v>18</v>
       </c>
-      <c r="C226">
-        <v>48</v>
+      <c r="C226" t="s">
+        <v>563</v>
       </c>
       <c r="D226">
         <v>2</v>
       </c>
       <c r="E226" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="B227" t="s">
         <v>18</v>
       </c>
-      <c r="C227">
-        <v>63.998046879999997</v>
+      <c r="C227" t="s">
+        <v>564</v>
       </c>
       <c r="D227">
         <v>2</v>
       </c>
       <c r="E227" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="B228" t="s">
         <v>18</v>
       </c>
-      <c r="C228">
-        <v>48</v>
+      <c r="C228" t="s">
+        <v>565</v>
       </c>
       <c r="D228">
         <v>2</v>
       </c>
       <c r="E228" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>49</v>
+        <v>459</v>
       </c>
       <c r="B229" t="s">
         <v>18</v>
       </c>
-      <c r="C229">
-        <v>48</v>
+      <c r="C229" t="s">
+        <v>564</v>
       </c>
       <c r="D229">
         <v>2</v>
       </c>
       <c r="E229" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="B230" t="s">
         <v>18</v>
       </c>
-      <c r="C230">
-        <v>63.998046879999997</v>
+      <c r="C230" t="s">
+        <v>563</v>
       </c>
       <c r="D230">
         <v>2</v>
       </c>
       <c r="E230" t="s">
-        <v>449</v>
+        <v>462</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="B231" t="s">
         <v>18</v>
       </c>
-      <c r="C231">
-        <v>48</v>
+      <c r="C231" t="s">
+        <v>563</v>
       </c>
       <c r="D231">
         <v>2</v>
       </c>
       <c r="E231" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="B232" t="s">
         <v>18</v>
       </c>
-      <c r="C232">
-        <v>48</v>
+      <c r="C232" t="s">
+        <v>565</v>
       </c>
       <c r="D232">
         <v>2</v>
       </c>
       <c r="E232" t="s">
-        <v>453</v>
+        <v>466</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="B233" t="s">
         <v>18</v>
       </c>
-      <c r="C233">
-        <v>63.998046879999997</v>
+      <c r="C233" t="s">
+        <v>563</v>
       </c>
       <c r="D233">
         <v>2</v>
       </c>
       <c r="E233" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>88</v>
+        <v>469</v>
       </c>
       <c r="B234" t="s">
         <v>18</v>
       </c>
-      <c r="C234">
-        <v>48</v>
+      <c r="C234" t="s">
+        <v>563</v>
       </c>
       <c r="D234">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E234" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="B235" t="s">
         <v>18</v>
       </c>
-      <c r="C235">
-        <v>63.998046879999997</v>
+      <c r="C235" t="s">
+        <v>564</v>
       </c>
       <c r="D235">
         <v>2</v>
       </c>
       <c r="E235" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="B236" t="s">
         <v>18</v>
       </c>
-      <c r="C236">
-        <v>63.998046879999997</v>
+      <c r="C236" t="s">
+        <v>563</v>
       </c>
       <c r="D236">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E236" t="s">
-        <v>460</v>
+        <v>474</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>97</v>
+        <v>475</v>
       </c>
       <c r="B237" t="s">
         <v>18</v>
       </c>
-      <c r="C237">
-        <v>48</v>
+      <c r="C237" t="s">
+        <v>563</v>
       </c>
       <c r="D237">
         <v>2</v>
       </c>
       <c r="E237" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>81</v>
+        <v>477</v>
       </c>
       <c r="B238" t="s">
         <v>18</v>
       </c>
-      <c r="C238">
-        <v>48</v>
+      <c r="C238" t="s">
+        <v>565</v>
       </c>
       <c r="D238">
         <v>2</v>
       </c>
       <c r="E238" t="s">
-        <v>462</v>
+        <v>478</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>463</v>
+        <v>479</v>
       </c>
       <c r="B239" t="s">
         <v>18</v>
       </c>
-      <c r="C239">
-        <v>63.998046879999997</v>
+      <c r="C239" t="s">
+        <v>563</v>
       </c>
       <c r="D239">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E239" t="s">
-        <v>464</v>
+        <v>480</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>377</v>
+        <v>481</v>
       </c>
       <c r="B240" t="s">
         <v>18</v>
       </c>
-      <c r="C240">
-        <v>48</v>
+      <c r="C240" t="s">
+        <v>565</v>
       </c>
       <c r="D240">
         <v>2</v>
       </c>
       <c r="E240" t="s">
-        <v>465</v>
+        <v>482</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="B241" t="s">
         <v>18</v>
       </c>
-      <c r="C241">
-        <v>48</v>
+      <c r="C241" t="s">
+        <v>564</v>
       </c>
       <c r="D241">
         <v>2</v>
       </c>
       <c r="E241" t="s">
-        <v>467</v>
+        <v>484</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>468</v>
+        <v>485</v>
       </c>
       <c r="B242" t="s">
         <v>18</v>
       </c>
-      <c r="C242">
-        <v>63.998046879999997</v>
+      <c r="C242" t="s">
+        <v>564</v>
       </c>
       <c r="D242">
         <v>2</v>
       </c>
       <c r="E242" t="s">
-        <v>469</v>
+        <v>486</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>470</v>
+        <v>26</v>
       </c>
       <c r="B243" t="s">
         <v>18</v>
       </c>
-      <c r="C243">
-        <v>48</v>
+      <c r="C243" t="s">
+        <v>563</v>
       </c>
       <c r="D243">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E243" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>472</v>
+        <v>488</v>
       </c>
       <c r="B244" t="s">
         <v>18</v>
       </c>
-      <c r="C244">
-        <v>48</v>
+      <c r="C244" t="s">
+        <v>564</v>
       </c>
       <c r="D244">
         <v>2</v>
       </c>
       <c r="E244" t="s">
-        <v>473</v>
+        <v>489</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>206</v>
+        <v>490</v>
       </c>
       <c r="B245" t="s">
         <v>18</v>
       </c>
-      <c r="C245">
-        <v>48</v>
+      <c r="C245" t="s">
+        <v>565</v>
       </c>
       <c r="D245">
         <v>2</v>
       </c>
       <c r="E245" t="s">
-        <v>474</v>
+        <v>491</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c r="B246" t="s">
         <v>18</v>
       </c>
-      <c r="C246">
-        <v>127.9960938</v>
+      <c r="C246" t="s">
+        <v>564</v>
       </c>
       <c r="D246">
         <v>2</v>
       </c>
       <c r="E246" t="s">
-        <v>476</v>
+        <v>493</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>477</v>
+        <v>494</v>
       </c>
       <c r="B247" t="s">
         <v>18</v>
       </c>
-      <c r="C247">
-        <v>64</v>
+      <c r="C247" t="s">
+        <v>570</v>
       </c>
       <c r="D247">
         <v>2</v>
       </c>
       <c r="E247" t="s">
-        <v>478</v>
+        <v>495</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="B248" t="s">
         <v>18</v>
       </c>
-      <c r="C248">
-        <v>48</v>
+      <c r="C248" t="s">
+        <v>563</v>
       </c>
       <c r="D248">
         <v>2</v>
       </c>
       <c r="E248" t="s">
-        <v>480</v>
+        <v>497</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>481</v>
+        <v>498</v>
       </c>
       <c r="B249" t="s">
         <v>18</v>
       </c>
-      <c r="C249">
-        <v>64</v>
+      <c r="C249" t="s">
+        <v>563</v>
       </c>
       <c r="D249">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E249" t="s">
-        <v>482</v>
+        <v>499</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="B250" t="s">
         <v>18</v>
       </c>
-      <c r="C250">
-        <v>127.9960938</v>
+      <c r="C250" t="s">
+        <v>563</v>
       </c>
       <c r="D250">
         <v>2</v>
       </c>
       <c r="E250" t="s">
-        <v>484</v>
+        <v>501</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="B251" t="s">
         <v>18</v>
       </c>
-      <c r="C251">
-        <v>64</v>
+      <c r="C251" t="s">
+        <v>564</v>
       </c>
       <c r="D251">
         <v>2</v>
       </c>
       <c r="E251" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>487</v>
+        <v>504</v>
       </c>
       <c r="B252" t="s">
         <v>18</v>
       </c>
-      <c r="C252">
-        <v>48</v>
+      <c r="C252" t="s">
+        <v>564</v>
       </c>
       <c r="D252">
         <v>2</v>
       </c>
       <c r="E252" t="s">
-        <v>488</v>
+        <v>505</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>489</v>
+        <v>506</v>
       </c>
       <c r="B253" t="s">
         <v>18</v>
       </c>
-      <c r="C253">
-        <v>48</v>
+      <c r="C253" t="s">
+        <v>563</v>
       </c>
       <c r="D253">
         <v>2</v>
       </c>
       <c r="E253" t="s">
-        <v>490</v>
+        <v>507</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="B254" t="s">
         <v>18</v>
       </c>
-      <c r="C254">
-        <v>127.9960938</v>
+      <c r="C254" t="s">
+        <v>564</v>
       </c>
       <c r="D254">
         <v>2</v>
       </c>
       <c r="E254" t="s">
-        <v>492</v>
+        <v>509</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="B255" t="s">
         <v>18</v>
       </c>
-      <c r="C255">
-        <v>48</v>
+      <c r="C255" t="s">
+        <v>564</v>
       </c>
       <c r="D255">
         <v>2</v>
       </c>
       <c r="E255" t="s">
-        <v>494</v>
+        <v>511</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>495</v>
+        <v>512</v>
       </c>
       <c r="B256" t="s">
         <v>18</v>
       </c>
-      <c r="C256">
-        <v>48</v>
+      <c r="C256" t="s">
+        <v>563</v>
       </c>
       <c r="D256">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E256" t="s">
-        <v>496</v>
+        <v>513</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>497</v>
+        <v>514</v>
       </c>
       <c r="B257" t="s">
         <v>18</v>
       </c>
-      <c r="C257">
-        <v>63.998046879999997</v>
+      <c r="C257" t="s">
+        <v>563</v>
       </c>
       <c r="D257">
         <v>2</v>
       </c>
       <c r="E257" t="s">
-        <v>498</v>
+        <v>515</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>499</v>
+        <v>516</v>
       </c>
       <c r="B258" t="s">
         <v>18</v>
       </c>
-      <c r="C258">
-        <v>48</v>
+      <c r="C258" t="s">
+        <v>563</v>
       </c>
       <c r="D258">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E258" t="s">
-        <v>500</v>
+        <v>517</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>501</v>
+        <v>518</v>
       </c>
       <c r="B259" t="s">
         <v>18</v>
       </c>
-      <c r="C259">
-        <v>48</v>
+      <c r="C259" t="s">
+        <v>565</v>
       </c>
       <c r="D259">
         <v>2</v>
       </c>
       <c r="E259" t="s">
-        <v>502</v>
+        <v>519</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>503</v>
+        <v>520</v>
       </c>
       <c r="B260" t="s">
         <v>18</v>
       </c>
-      <c r="C260">
-        <v>127.9960938</v>
+      <c r="C260" t="s">
+        <v>564</v>
       </c>
       <c r="D260">
         <v>2</v>
       </c>
       <c r="E260" t="s">
-        <v>504</v>
+        <v>521</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>505</v>
+        <v>522</v>
       </c>
       <c r="B261" t="s">
         <v>18</v>
       </c>
-      <c r="C261">
-        <v>48</v>
+      <c r="C261" t="s">
+        <v>563</v>
       </c>
       <c r="D261">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E261" t="s">
-        <v>506</v>
+        <v>523</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>507</v>
+        <v>46</v>
       </c>
       <c r="B262" t="s">
         <v>18</v>
       </c>
-      <c r="C262">
-        <v>127.9960938</v>
+      <c r="C262" t="s">
+        <v>563</v>
       </c>
       <c r="D262">
         <v>2</v>
       </c>
       <c r="E262" t="s">
-        <v>508</v>
+        <v>524</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>509</v>
+        <v>525</v>
       </c>
       <c r="B263" t="s">
         <v>18</v>
       </c>
-      <c r="C263">
-        <v>64</v>
+      <c r="C263" t="s">
+        <v>564</v>
       </c>
       <c r="D263">
         <v>2</v>
       </c>
       <c r="E263" t="s">
-        <v>510</v>
+        <v>526</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>511</v>
+        <v>527</v>
       </c>
       <c r="B264" t="s">
         <v>18</v>
       </c>
-      <c r="C264">
-        <v>63.998046879999997</v>
+      <c r="C264" t="s">
+        <v>565</v>
       </c>
       <c r="D264">
         <v>2</v>
       </c>
       <c r="E264" t="s">
-        <v>512</v>
+        <v>528</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>26</v>
+        <v>529</v>
       </c>
       <c r="B265" t="s">
         <v>18</v>
       </c>
-      <c r="C265">
-        <v>48</v>
+      <c r="C265" t="s">
+        <v>563</v>
       </c>
       <c r="D265">
         <v>2</v>
       </c>
       <c r="E265" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>514</v>
+        <v>531</v>
       </c>
       <c r="B266" t="s">
         <v>18</v>
       </c>
-      <c r="C266">
-        <v>64</v>
+      <c r="C266" t="s">
+        <v>563</v>
       </c>
       <c r="D266">
         <v>2</v>
       </c>
       <c r="E266" t="s">
-        <v>515</v>
+        <v>532</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>516</v>
+        <v>533</v>
       </c>
       <c r="B267" t="s">
-        <v>18</v>
-      </c>
-      <c r="C267">
-        <v>127.9960938</v>
+        <v>1</v>
+      </c>
+      <c r="C267" t="s">
+        <v>559</v>
       </c>
       <c r="D267">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E267" t="s">
-        <v>517</v>
+        <v>534</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>518</v>
+        <v>535</v>
       </c>
       <c r="B268" t="s">
-        <v>18</v>
-      </c>
-      <c r="C268">
-        <v>63.998046879999997</v>
+        <v>1</v>
+      </c>
+      <c r="C268" t="s">
+        <v>567</v>
       </c>
       <c r="D268">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E268" t="s">
-        <v>519</v>
+        <v>536</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="B269" t="s">
-        <v>18</v>
-      </c>
-      <c r="C269">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="C269" t="s">
+        <v>559</v>
       </c>
       <c r="D269">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E269" t="s">
-        <v>521</v>
+        <v>538</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>522</v>
+        <v>539</v>
       </c>
       <c r="B270" t="s">
-        <v>18</v>
-      </c>
-      <c r="C270">
-        <v>48</v>
+        <v>12</v>
+      </c>
+      <c r="C270" t="s">
+        <v>562</v>
       </c>
       <c r="D270">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E270" t="s">
-        <v>523</v>
+        <v>540</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>524</v>
+        <v>541</v>
       </c>
       <c r="B271" t="s">
-        <v>18</v>
-      </c>
-      <c r="C271">
-        <v>48</v>
+        <v>12</v>
+      </c>
+      <c r="C271" t="s">
+        <v>561</v>
       </c>
       <c r="D271">
         <v>1</v>
       </c>
       <c r="E271" t="s">
-        <v>525</v>
+        <v>542</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>526</v>
+        <v>543</v>
       </c>
       <c r="B272" t="s">
         <v>18</v>
       </c>
-      <c r="C272">
-        <v>48</v>
+      <c r="C272" t="s">
+        <v>560</v>
       </c>
       <c r="D272">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E272" t="s">
-        <v>527</v>
+        <v>544</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>528</v>
+        <v>545</v>
       </c>
       <c r="B273" t="s">
         <v>18</v>
       </c>
-      <c r="C273">
-        <v>63.998046879999997</v>
+      <c r="C273" t="s">
+        <v>560</v>
       </c>
       <c r="D273">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E273" t="s">
-        <v>529</v>
+        <v>546</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>530</v>
+        <v>547</v>
       </c>
       <c r="B274" t="s">
         <v>18</v>
       </c>
-      <c r="C274">
-        <v>63.998046879999997</v>
+      <c r="C274" t="s">
+        <v>561</v>
       </c>
       <c r="D274">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E274" t="s">
-        <v>531</v>
+        <v>548</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="B275" t="s">
         <v>18</v>
       </c>
-      <c r="C275">
-        <v>48</v>
+      <c r="C275" t="s">
+        <v>560</v>
       </c>
       <c r="D275">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E275" t="s">
-        <v>533</v>
+        <v>550</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>534</v>
+        <v>551</v>
       </c>
       <c r="B276" t="s">
         <v>18</v>
       </c>
-      <c r="C276">
-        <v>63.998046879999997</v>
+      <c r="C276" t="s">
+        <v>559</v>
       </c>
       <c r="D276">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E276" t="s">
-        <v>535</v>
+        <v>552</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>536</v>
+        <v>553</v>
       </c>
       <c r="B277" t="s">
-        <v>18</v>
-      </c>
-      <c r="C277">
-        <v>63.998046879999997</v>
+        <v>12</v>
+      </c>
+      <c r="C277" t="s">
+        <v>562</v>
       </c>
       <c r="D277">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E277" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A278" t="s">
-        <v>538</v>
-      </c>
-      <c r="B278" t="s">
-        <v>18</v>
-      </c>
-      <c r="C278">
-        <v>48</v>
-      </c>
-      <c r="D278">
-        <v>2</v>
-      </c>
-      <c r="E278" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A279" t="s">
-        <v>540</v>
-      </c>
-      <c r="B279" t="s">
-        <v>18</v>
-      </c>
-      <c r="C279">
-        <v>48</v>
-      </c>
-      <c r="D279">
-        <v>2</v>
-      </c>
-      <c r="E279" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A280" t="s">
-        <v>542</v>
-      </c>
-      <c r="B280" t="s">
-        <v>18</v>
-      </c>
-      <c r="C280">
-        <v>48</v>
-      </c>
-      <c r="D280">
-        <v>2</v>
-      </c>
-      <c r="E280" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A281" t="s">
-        <v>544</v>
-      </c>
-      <c r="B281" t="s">
-        <v>18</v>
-      </c>
-      <c r="C281">
-        <v>127.9960938</v>
-      </c>
-      <c r="D281">
-        <v>2</v>
-      </c>
-      <c r="E281" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A282" t="s">
-        <v>546</v>
-      </c>
-      <c r="B282" t="s">
-        <v>18</v>
-      </c>
-      <c r="C282">
-        <v>63.998046879999997</v>
-      </c>
-      <c r="D282">
-        <v>2</v>
-      </c>
-      <c r="E282" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A283" t="s">
-        <v>548</v>
-      </c>
-      <c r="B283" t="s">
-        <v>18</v>
-      </c>
-      <c r="C283">
-        <v>48</v>
-      </c>
-      <c r="D283">
-        <v>2</v>
-      </c>
-      <c r="E283" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A284" t="s">
-        <v>46</v>
-      </c>
-      <c r="B284" t="s">
-        <v>18</v>
-      </c>
-      <c r="C284">
-        <v>48</v>
-      </c>
-      <c r="D284">
-        <v>2</v>
-      </c>
-      <c r="E284" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A285" t="s">
-        <v>551</v>
-      </c>
-      <c r="B285" t="s">
-        <v>18</v>
-      </c>
-      <c r="C285">
-        <v>63.998046879999997</v>
-      </c>
-      <c r="D285">
-        <v>2</v>
-      </c>
-      <c r="E285" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A286" t="s">
-        <v>553</v>
-      </c>
-      <c r="B286" t="s">
-        <v>18</v>
-      </c>
-      <c r="C286">
-        <v>127.9960938</v>
-      </c>
-      <c r="D286">
-        <v>2</v>
-      </c>
-      <c r="E286" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A287" t="s">
-        <v>555</v>
-      </c>
-      <c r="B287" t="s">
-        <v>18</v>
-      </c>
-      <c r="C287">
-        <v>48</v>
-      </c>
-      <c r="D287">
-        <v>2</v>
-      </c>
-      <c r="E287" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A288" t="s">
-        <v>557</v>
-      </c>
-      <c r="B288" t="s">
-        <v>18</v>
-      </c>
-      <c r="C288">
-        <v>48</v>
-      </c>
-      <c r="D288">
-        <v>2</v>
-      </c>
-      <c r="E288" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A289" t="s">
-        <v>559</v>
-      </c>
-      <c r="B289" t="s">
-        <v>1</v>
-      </c>
-      <c r="C289">
-        <v>8</v>
-      </c>
-      <c r="D289">
-        <v>1</v>
-      </c>
-      <c r="E289" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A290" t="s">
-        <v>561</v>
-      </c>
-      <c r="B290" t="s">
-        <v>1</v>
-      </c>
-      <c r="C290">
-        <v>4</v>
-      </c>
-      <c r="D290">
-        <v>1</v>
-      </c>
-      <c r="E290" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A291" t="s">
-        <v>563</v>
-      </c>
-      <c r="B291" t="s">
-        <v>1</v>
-      </c>
-      <c r="C291">
-        <v>8</v>
-      </c>
-      <c r="D291">
-        <v>1</v>
-      </c>
-      <c r="E291" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A292" t="s">
-        <v>565</v>
-      </c>
-      <c r="B292" t="s">
-        <v>12</v>
-      </c>
-      <c r="C292">
-        <v>24</v>
-      </c>
-      <c r="D292">
-        <v>1</v>
-      </c>
-      <c r="E292" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A293" t="s">
-        <v>567</v>
-      </c>
-      <c r="B293" t="s">
-        <v>12</v>
-      </c>
-      <c r="C293">
-        <v>32</v>
-      </c>
-      <c r="D293">
-        <v>1</v>
-      </c>
-      <c r="E293" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A294" t="s">
-        <v>569</v>
-      </c>
-      <c r="B294" t="s">
-        <v>18</v>
-      </c>
-      <c r="C294">
-        <v>16</v>
-      </c>
-      <c r="D294">
-        <v>1</v>
-      </c>
-      <c r="E294" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A295" t="s">
-        <v>571</v>
-      </c>
-      <c r="B295" t="s">
-        <v>18</v>
-      </c>
-      <c r="C295">
-        <v>16</v>
-      </c>
-      <c r="D295">
-        <v>1</v>
-      </c>
-      <c r="E295" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A296" t="s">
-        <v>573</v>
-      </c>
-      <c r="B296" t="s">
-        <v>18</v>
-      </c>
-      <c r="C296">
-        <v>31.999023439999998</v>
-      </c>
-      <c r="D296">
-        <v>1</v>
-      </c>
-      <c r="E296" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A297" t="s">
-        <v>575</v>
-      </c>
-      <c r="B297" t="s">
-        <v>18</v>
-      </c>
-      <c r="C297">
-        <v>16</v>
-      </c>
-      <c r="D297">
-        <v>1</v>
-      </c>
-      <c r="E297" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A298" t="s">
-        <v>577</v>
-      </c>
-      <c r="B298" t="s">
-        <v>18</v>
-      </c>
-      <c r="C298">
-        <v>8</v>
-      </c>
-      <c r="D298">
-        <v>1</v>
-      </c>
-      <c r="E298" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A299" t="s">
-        <v>579</v>
-      </c>
-      <c r="B299" t="s">
-        <v>580</v>
-      </c>
-      <c r="C299">
-        <v>62.598632809999998</v>
-      </c>
-      <c r="D299">
-        <v>1</v>
-      </c>
-      <c r="E299" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A300" t="s">
-        <v>582</v>
-      </c>
-      <c r="B300" t="s">
-        <v>12</v>
-      </c>
-      <c r="C300">
-        <v>24</v>
-      </c>
-      <c r="D300">
-        <v>1</v>
-      </c>
-      <c r="E300" t="s">
-        <v>583</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E300" xr:uid="{1A3679B1-22FB-4F47-82CA-80DBF18D622E}"/>
+  <autoFilter ref="A1:E277" xr:uid="{1A3679B1-22FB-4F47-82CA-80DBF18D622E}"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
